--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T15:37:21+00:00</t>
+    <t>2025-12-15T15:37:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T15:37:58+00:00</t>
+    <t>2026-02-09T11:09:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T11:09:38+00:00</t>
+    <t>2026-03-26T12:56:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-26T12:56:02+00:00</t>
+    <t>2026-03-27T08:00:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T08:00:01+00:00</t>
+    <t>2026-03-27T12:55:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T12:55:15+00:00</t>
+    <t>2026-03-27T14:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T14:42:15+00:00</t>
+    <t>2026-04-02T10:19:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T10:19:50+00:00</t>
+    <t>2026-04-09T13:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T13:07:19+00:00</t>
+    <t>2026-04-13T12:18:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T12:18:34+00:00</t>
+    <t>2026-04-14T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T12:56:47+00:00</t>
+    <t>2026-04-14T13:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T13:00:40+00:00</t>
+    <t>2026-04-14T13:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T13:24:37+00:00</t>
+    <t>2026-04-22T08:32:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:32:05+00:00</t>
+    <t>2026-04-22T13:26:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T13:26:00+00:00</t>
+    <t>2026-05-04T08:14:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:14:07+00:00</t>
+    <t>2026-05-13T07:14:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T07:14:42+00:00</t>
+    <t>2026-06-10T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T08:49:37+00:00</t>
+    <t>2026-06-10T08:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T08:50:04+00:00</t>
+    <t>2026-06-10T08:52:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T08:52:37+00:00</t>
+    <t>2026-06-16T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -99,13 +99,13 @@
     <t>Source</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-AdministrativeGender</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-AdministrativeGender|3.0.0</t>
   </si>
   <si>
     <t>Target</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender</t>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>Display</t>
@@ -114,13 +114,13 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-AdministrativeGender</t>
+    <t>http://terminology.hl7.org/CodeSystem/v3-AdministrativeGender|4.0.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>http://hl7.org/fhir/administrative-gender</t>
+    <t>http://hl7.org/fhir/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>M</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:17:05+00:00</t>
+    <t>2026-06-17T07:57:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:57:57+00:00</t>
+    <t>2026-06-17T09:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:34:17+00:00</t>
+    <t>2026-06-18T08:47:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:47:35+00:00</t>
+    <t>2026-06-18T09:44:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:44:31+00:00</t>
+    <t>2026-06-18T10:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:42:22+00:00</t>
+    <t>2026-06-18T10:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:44:43+00:00</t>
+    <t>2026-06-26T12:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:07:29+00:00</t>
+    <t>2026-06-30T14:53:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:53:19+00:00</t>
+    <t>2026-07-02T14:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T14:54:00+00:00</t>
+    <t>2026-07-02T14:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T14:58:37+00:00</t>
+    <t>2026-07-07T15:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T15:31:37+00:00</t>
+    <t>2026-07-07T15:40:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T15:40:33+00:00</t>
+    <t>2026-07-15T11:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T11:54:19+00:00</t>
+    <t>2026-07-17T07:40:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T07:40:05+00:00</t>
+    <t>2026-07-17T13:13:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T13:13:19+00:00</t>
+    <t>2026-07-20T12:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T12:36:25+00:00</t>
+    <t>2026-07-31T12:50:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:50:31+00:00</t>
+    <t>2026-07-31T12:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/cm-v3-administrative-gender.xlsx
+++ b/main/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:55:21+00:00</t>
+    <t>2026-07-31T13:43:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
